--- a/references PV interneurons, ketamin, MDD.xlsx
+++ b/references PV interneurons, ketamin, MDD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/226c0ae47ee88382/Dokumente/_daten/PERSOENL/bewerbungen/bio-energie/MED UNI WIEN - Medizinische Informatik/Introduction to Neuroscience/Group Topic 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/226c0ae47ee88382/Dokumente/_daten/PERSOENL/bewerbungen/bio-energie/MED UNI WIEN - Medizinische Informatik/Introduction to Neuroscience/Group Topic 1/literature/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="341" documentId="8_{AB0CBE37-26A3-4530-A113-FB029F5D389C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DB86819-17ED-428C-B823-001C964D9942}"/>
+  <xr:revisionPtr revIDLastSave="346" documentId="8_{AB0CBE37-26A3-4530-A113-FB029F5D389C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF39ABD7-24BC-49FA-A890-09B103A8F061}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B732B695-7EFD-4D52-AA78-EF8E41886C78}"/>
   </bookViews>
@@ -206,9 +206,6 @@
     <t>Advanced Science; Weinheim Bd. 11, Ausg. 5</t>
   </si>
   <si>
-    <t>articles (and authors) mentioned in "further research questions"</t>
-  </si>
-  <si>
     <t>10.1038/s41593-020-0621-y</t>
   </si>
   <si>
@@ -300,6 +297,9 @@
       </rPr>
       <t>(key words for selection: ketamine, MDD, PV interneurons)</t>
     </r>
+  </si>
+  <si>
+    <t>articles (and authors) mentioned in "group project topics" and "further research questions"</t>
   </si>
 </sst>
 </file>
@@ -487,7 +487,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -514,56 +514,51 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="17" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -572,20 +567,23 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -930,316 +928,315 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="17" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="81.5546875" style="37" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="81.5546875" style="34" customWidth="1"/>
     <col min="6" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="32" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="12">
+        <v>45051</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.35">
+      <c r="A3" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B3" s="12">
         <v>44034</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C3" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E3" s="33" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+    <row r="4" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="12">
+        <v>43983</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B5" s="24">
         <v>43245</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C5" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D5" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E5" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="12">
+        <v>42136</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="33"/>
+    </row>
+    <row r="8" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="12">
+        <v>45931</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="15" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="13">
-        <v>42136</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="36"/>
-    </row>
-    <row r="6" spans="1:5" s="15" customFormat="1" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="13">
-        <v>45931</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="36" t="s">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="B9" s="12">
         <v>45817</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E9" s="34" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="10" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B10" s="12">
         <v>45513</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C10" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E10" s="34" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="11" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B11" s="12">
         <v>45323</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C11" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D11" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E11" s="34" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="12" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B12" s="12">
         <v>45084</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C12" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E12" s="34" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="15" customFormat="1" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="13">
-        <v>45051</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B13" s="12">
         <v>45047</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C13" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E13" s="34" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B14" s="12">
         <v>44580</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E14" s="34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+    <row r="15" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B15" s="12">
         <v>44256</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E15" s="34" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="15" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="13">
-        <v>43983</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="11" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="12">
         <v>43444</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="35" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D17" s="14"/>
+      <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:5" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A18" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="37"/>
+      <c r="A18" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="23"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:5" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A19" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="37"/>
+      <c r="A19" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="34"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="14"/>
+        <v>62</v>
+      </c>
+      <c r="D20" s="13"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:E16">
-    <sortCondition descending="1" ref="B6:B16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:E16">
+    <sortCondition descending="1" ref="B8:B16"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D12" r:id="rId1" display="https://doi.org/10.1177/15353702231170007" xr:uid="{AA034294-ECA7-4781-85F7-694E50A72EDA}"/>
-    <hyperlink ref="D7" r:id="rId2" display="https://doi.org/10.1371/journal.pcbi.1013118" xr:uid="{A498207A-7C73-4888-872F-E44FA9BE5A12}"/>
-    <hyperlink ref="E14" r:id="rId3" tooltip="Suche nach: Autor / Beteiligte = Eggerstorfer, Benjamin" display="https://repositorium.meduniwien.ac.at/obvumwhs/search?operation=searchRetrieve&amp;query=bib.personalName%3D%22Eggerstorfer%2C%20Benjamin%22%20and%20vl.domain%3Dobvumw%20sortBy%20dc.title%2Fasc" xr:uid="{A63F220F-53D8-4AD0-BE3A-BE950B067C30}"/>
-    <hyperlink ref="D14" r:id="rId4" display="https://resolver.obvsg.at/urn:nbn:at:at-ubmuw:1-34848" xr:uid="{4B103884-8D12-4E42-A53F-EA1C1FB822C4}"/>
+    <hyperlink ref="D13" r:id="rId1" display="https://doi.org/10.1177/15353702231170007" xr:uid="{AA034294-ECA7-4781-85F7-694E50A72EDA}"/>
+    <hyperlink ref="D9" r:id="rId2" display="https://doi.org/10.1371/journal.pcbi.1013118" xr:uid="{A498207A-7C73-4888-872F-E44FA9BE5A12}"/>
+    <hyperlink ref="E15" r:id="rId3" tooltip="Suche nach: Autor / Beteiligte = Eggerstorfer, Benjamin" display="https://repositorium.meduniwien.ac.at/obvumwhs/search?operation=searchRetrieve&amp;query=bib.personalName%3D%22Eggerstorfer%2C%20Benjamin%22%20and%20vl.domain%3Dobvumw%20sortBy%20dc.title%2Fasc" xr:uid="{A63F220F-53D8-4AD0-BE3A-BE950B067C30}"/>
+    <hyperlink ref="D15" r:id="rId4" display="https://resolver.obvsg.at/urn:nbn:at:at-ubmuw:1-34848" xr:uid="{4B103884-8D12-4E42-A53F-EA1C1FB822C4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
